--- a/wildberries_full_catalog.xlsx
+++ b/wildberries_full_catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,316 +486,283 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/239833866/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488386749/detail.aspx</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>239833866</v>
+        <v>488386749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
+          <t>Пальто длинное оверсайз весна-осень в полоску</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8278</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Окунитесь в стиль и комфорт, выбирая женское пальто для сезона весна-осень. Состав изделия: шерсть - 57%, вискоза - 36%, полиэстер - 7%. Длина пальто по спинке - 63 см. Длина рукава - 63,5 см. Это короткое демисезонное пальто с воротником-стойкой станет вашим верным спутником в любое время года. Однобортное пальто прямого кроя. Воротник-стойка защитит Вас от прохладного ветра, втачные рукава обеспечивают лучшую посадку и комфорт при движении, глубокие карманы с листочкой, отделанные декоративной отстрочкой, придают уникальность, застежкой служат пришивные кнопки. Теплое укороченное пальто привносит в образ изысканность, согреет вас даже в прохладные дни. Дизайнерская вещь подходит для девушек и женщин, ценящих как кэжуал стиль, так и офисную классику. Кофейный-коричневый цвет подойдет к любому образу и станет незаменимой вещью в гардеробе автоледи.
-Кашемировое внимание привлекается длинной линией и модным силуэтом - настоящее утончение 2026 года! Вариации размеров делают изделие доступным даже для подростков и невысоких девочек.
-Будьте уверены: ваше новое ворсовое шерстяное полупальто не только подчеркнет вашу индивидуальность, но и подарит тепло. Смешивайте его с другими модными предметами вашего гардероба – ведь это ключ к созданию стильного ансамбля. Натуральная ткань обеспечивает уют при каждом ношении.
-Ткань имеет ворсистую фактуру, так как в составе большой процент шерсти, из-за этого возможно прилипание волокна, шерсти животных и пыли. Ткань не скатывается, сохраняет цвет и форму. В процессе носки ворс ткани поднимается, поэтому рекомендуем очистить ворс липким роликом, пройтись велюровой щеткой по направлению ворса. Вся продукция бренда КОРЕССИ произведена по высоким стандартам, отшивается на новейшем швейном оборудовании, проходит качественный контроль. Производство Россия. Будем признательны оставленному отзыву! Приятных покупок!
-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://basket-15.wbcontent.net/vol2398/part239833/239833866/images/big/1.webp,https://basket-15.wbcontent.net/vol2398/part239833/239833866/images/big/2.webp,https://basket-15.wbcontent.net/vol2398/part239833/239833866/images/big/3.webp,https://basket-15.wbcontent.net/vol2398/part239833/239833866/images/big/4.webp,https://basket-15.wbcontent.net/vol2398/part239833/239833866/images/big/5.webp</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Состав: шерсть; вискоза; полиэстер | Цвет: коричневый; кофейный | Пол: Женский | Сезон: Демисезон | Вид застежки: кнопки | Рост модели на фото: 164 см | Параметры модели на фото (ОГ-ОТ-ОБ): 83-60-89 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Материал подкладки: полиэстер | Покрой: прямой | Тип карманов: прорезные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: декоративная отстрочка; воротник стойка; карманы | Особенности модели: однобортная; ветрозащита; износостойкость | Уход за вещами: деликатная химическая чистка; допускается отпаривание | Комплектация: Пальто - 1 шт; Упаковочная сумка-чемодан | Страна производства: Россия</t>
-        </is>
-      </c>
+        <v>4204</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coressi</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/26796</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>42, 44, 46, 48, 50, 52, 54</t>
+          <t>S, M, L, XL</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>166</v>
+        <v>388</v>
       </c>
       <c r="L2" t="n">
         <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>1840</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/174345731/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/742426015/detail.aspx</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174345731</v>
+        <v>742426015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Пальто длинное демисезонное оверсайз</t>
+          <t>Пальто оверсайз длинное весеннее</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4932</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Пальто женское — идеальный выбор для модных женщин, желающих подчеркнуть свой стиль в любое время года. Пальто женское весна-осень — это легкое и универсальное решение для прохладных дней межсезонья. Весенние модели выглядят свежо и легко, а осенние варианты, выполненные из шерсти и драпа, дарят уют и тепло. Демисезонное пальто — незаменимый элемент гардероба для периодов весна-осень и осень-зима, что позволяет подобрать подходящую модель для любого сезона.
-Осенние модели отличаются стильным дизайном и практичностью. Теплое, утепленное изделие согреет в холодную погоду, а ткань из шерсти с натуральным утеплителем отлично подходит даже для зимних дней. Однобортное пальто с поясом и пуговицами создаёт комфорт и элегантный силуэт.
-Модели оверсайз и плюс сайз подойдут для полных женщин и беременных, обеспечивая свободу движений. Для подростков и молодых девушек представлены молодежные и стильные модели в духе Pinterest, которые подчеркивают индивидуальность и актуальность модных тенденций.
-Пальто с английским воротником, качественной подкладкой и шерстяным утеплителем подчёркивают хороший вкус. Драповое пальто — классика, проверенная временем, отличается долговечностью и высоким качеством. Также в ассортименте есть пальто на запах, которые отлично подходят для еврозимы — лёгкие, уютные и комфортные при разной погоде.
-В коллекции представлены как длинные, так и макси модели. Длинное пальто выглядит элегантно и утонченно, а удлиненное миди — стильный вариант для тех, кто ценит баланс между модой и удобством. Прямой и приталенный крой подчёркивает фигуру и формирует женственный силуэт.
-Каждое изделие дополнено удобными глубокими карманами, а рукава со спущенной линией плеча обеспечивают свободу движений. Универсальная модель помогает легко собирать образы в стиле casual, винтаж или классика. В ассортименте есть дизайнерская верхняя одежда больших размеров и модели для невысоких девушек — можно подобрать вариант под любой запрос и стиль.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://basket-12.wbcontent.net/vol1743/part174345/174345731/images/big/1.webp,https://basket-12.wbcontent.net/vol1743/part174345/174345731/images/big/2.webp,https://basket-12.wbcontent.net/vol1743/part174345/174345731/images/big/3.webp,https://basket-12.wbcontent.net/vol1743/part174345/174345731/images/big/4.webp,https://basket-12.wbcontent.net/vol1743/part174345/174345731/images/big/5.webp</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Состав: шерсть 60%; вискоза 40% | Цвет: бежевый | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы; пояс | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 42-44 | Размер на модели: 44 | Утеплитель: шерсть | Температурный режим: от +10 °C до -5 °C | Материал подкладки: полиэстер 100% | Покрой: оверсайз | Тип карманов: накладные | Тип рукава: длинные | Опции капюшона: нет | Опции опушки: нет | Декоративные элементы: пояс | Особенности модели: для высоких | Уход за вещами: деликатная стирка | Комплектация: пальто; пояс | Страна производства: Киргизия</t>
-        </is>
-      </c>
+        <v>4032</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Amore Wear</t>
+          <t>the nana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1335719</t>
+          <t>https://www.wildberries.ru/seller/236134</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44 (НА ФОТО), 48, 50, 52, 42, 58, 38, 40, 66</t>
+          <t>46, 48, 50, 60, 62</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>1101</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/488386749/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/203138526/detail.aspx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>488386749</v>
+        <v>203138526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Пальто длинное оверсайз весна-осень в полоску</t>
+          <t>Пальто классика</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4204</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>9900</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шикарное шерстяное полупальто идеально для носки в демисезонный период - весенний и осенний сезоны, а также еврозимой. Укороченная короткая модель выполнена из качественного драпового материала, в составе которого натуральная шерсть, и имеет подкладку из дышащей ткани. Модное изделие прямого кроя с классическим отложным воротником - стойкой, потайным внутренним карманом и длинными рукавами легкое, но при этом очень теплое.  Полупальто станет лучшим выбором демисезонной верхней одежды и будет радовать вас не один сезон! </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/1.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/2.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/3.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/4.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/5.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/6.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/7.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/8.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/9.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/10.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/11.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/12.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/13.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/14.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/15.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/16.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/17.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/18.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/19.webp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Состав: Натуральная шерсть; Кашемир | Цвет: серый | Пол: Мужской | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 184 см | Параметры модели на фото (ОГ-ОТ-ОБ): 102-91-101 | Размер на модели: 54 (52РФ) | Утеплитель: без утеплителя | Температурный режим: от -5°C до +15°С | Материал подкладки: текстиль | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Декоративные элементы: пуговицы | Особенности модели: ветрозащита | Уход за вещами: стирка запрещена; храните пальто на вешалке, что бы сохранить форму; допускается отпаривание</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HANBIYKE</t>
+          <t>Красный ананас</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1304162</t>
+          <t>https://www.wildberries.ru/seller/1316722</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>S, M, L, XL</t>
+          <t>48, 50, 52, 54, 56</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>196</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>119</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/287700029/detail.aspx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>497508666</v>
+        <v>287700029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Пальто шерстяное короткое жакет</t>
+          <t>Пальто шерстяное натуральное</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7509</v>
+        <v>11523</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lindo Gato</t>
+          <t>MAISON DAVID</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/626100</t>
+          <t>https://www.wildberries.ru/seller/528630</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M, L, XL</t>
+          <t>XS, S, M, L, XL</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
         <v>4.8</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/287700029/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488387894/detail.aspx</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>287700029</v>
+        <v>488387894</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Пальто шерстяное натуральное</t>
+          <t>Пальто весна-осень макси в полоску</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12495</v>
+        <v>4204</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MAISON DAVID</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/528630</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>XS, S, M, L, XL</t>
+          <t>L, M, S, XL</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>398</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/203138526/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/497508666/detail.aspx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>203138526</v>
+        <v>497508666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Пальто классика</t>
+          <t>Пальто шерстяное короткое жакет</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9900</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Шикарное шерстяное полупальто идеально для носки в демисезонный период - весенний и осенний сезоны, а также еврозимой. Укороченная короткая модель выполнена из качественного драпового материала, в составе которого натуральная шерсть, и имеет подкладку из дышащей ткани. Модное изделие прямого кроя с классическим отложным воротником - стойкой, потайным внутренним карманом и длинными рукавами легкое, но при этом очень теплое.  Полупальто станет лучшим выбором демисезонной верхней одежды и будет радовать вас не один сезон! </t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/1.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/2.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/3.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/4.webp,https://basket-13.wbcontent.net/vol2031/part203138/203138526/images/big/5.webp</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Состав: Натуральная шерсть; Кашемир | Цвет: серый | Пол: Мужской | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 184 см | Параметры модели на фото (ОГ-ОТ-ОБ): 102-91-101 | Размер на модели: 54 (52РФ) | Утеплитель: без утеплителя | Температурный режим: от -5°C до +15°С | Материал подкладки: текстиль | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Декоративные элементы: пуговицы | Особенности модели: ветрозащита | Уход за вещами: стирка запрещена; храните пальто на вешалке, что бы сохранить форму; допускается отпаривание</t>
-        </is>
-      </c>
+        <v>7509</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Красный ананас</t>
+          <t>Lindo Gato</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/1316722</t>
+          <t>https://www.wildberries.ru/seller/626100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48, 50, 52, 54, 56</t>
+          <t>M, L, XL</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>197</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
         <v>4.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2608</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -813,7 +780,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9853</v>
+        <v>10100</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -834,13 +801,4530 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>4.6</v>
       </c>
       <c r="M8" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/500291585/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>500291585</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Двубортное пальто из драпа с добавлением шерсти</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4128</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SELA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/5862</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>L, M, XL, S, XS</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>99</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/319079863/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>319079863</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11625</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/255231</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>L, M, S</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>14</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/516995752/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>516995752</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Пальто осеннее длинное</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9184</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MÁS</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1192923</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>328</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M11" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/481144243/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>481144243</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>22140</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRIUMF ST</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/312039</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>42, 46, 52</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/257388507/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>257388507</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное классика</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10373</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шикарное шерстяное полупальто идеально для носки в демисезонный период - весенний и осенний сезоны, а также еврозимой. Укороченная короткая модель выполнена из качественного драпового материала, в составе которого натуральная шерсть, и имеет подкладку из дышащей ткани. Модное изделие прямого кроя с классическим английским воротником, потайным внутренним карманом и длинными рукавами легкое, но при этом очень теплое. </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/1.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/2.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/3.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/4.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/5.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/6.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/7.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/8.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/9.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/10.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/11.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/12.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/13.webp,https://basket-16.wbcontent.net/vol2573/part257388/257388507/images/big/14.webp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Состав: Натуральная шерсть; Кашемир | Цвет: темно-синий | Пол: Мужской | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 184 см | Параметры модели на фото (ОГ-ОТ-ОБ): 102-91-101 | Размер на модели: 54 (52РФ) | Утеплитель: без утеплителя | Температурный режим: от -5°C до +15°С | Материал подкладки: текстиль | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: пуговицы | Особенности модели: дышащий материал; драпировка | Уход за вещами: стирка запрещена; храните пальто на вешалке, что бы сохранить форму; допускается отпаривание</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Красный ананас</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1316722</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>165</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/366417625/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>366417625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8804</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>27</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/277883751/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>277883751</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Полупальто шерстяное</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8030</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Серое полупальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в деловом стиле — удачное решение для офисного гардероба. Это сдержанная элегантность, уверенность и профессионализм. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbcontent.net/vol2778/part277883/277883751/images/big/1.webp,https://basket-17.wbcontent.net/vol2778/part277883/277883751/images/big/2.webp,https://basket-17.wbcontent.net/vol2778/part277883/277883751/images/big/3.webp,https://basket-17.wbcontent.net/vol2778/part277883/277883751/images/big/4.webp,https://basket-17.wbcontent.net/vol2778/part277883/277883751/images/big/5.webp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Состав: шерсть натуральная 100% | Цвет: серый | Сезон: демисезон | Рост модели на фото: 175 см | Температурный режим: от -5 °C до +10 °C | Покрой: прямой | Воротник: отложной | Тип карманов: прорезные | Особенности модели: Без капюшона, теплый | Пол: Женский | Уход за вещами: Химическая стирка; стирка запрещена; отбеливание запрещено | Комплектация: 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>S, M, L, XS, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/305471553/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>305471553</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12456</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женское пальто Befur – идеальный выбор для прохладной осени и ранней весны.  Модель выполнена из качественной ткани с добавлением натуральной шерсти, что обеспечивает комфорт и приятные тактильные ощущения. Двубортный крой с ветрозащитой надежно защитит от непогоды, а диагональный рисунок придает пальто стильный и современный вид. Прямой крой рукавов и прорезные карманы делают модель удобной в носке. Изготовленное из прочной смеси натуральной шерсти (80%) и полиэстера (20%), оно обеспечит вам комфорт и тепло в осенне-весенний период. Женское  пальто отлично подойдет как на весну, так и на осень и даже на начало зимы! Благодаря своему крою и размерной сетке идеально сядет на высоких и невысоких девушек и на беременных, будущих мам . Удобный пояс при желании легко сделает приталенное пальто. Верхняя одежда хорошо смотрится как со спортивными кроссовками, так и с модными высокими сапогами или с грубыми ботинками.
+Пальто Befur – это сочетание практичности, элегантности и комфорта.
+Обращайте внимание на оригинальный лейбл "Befur" и уникальный QR-код "Честный знак".
+Внимание! Если вам пришло изделие с браком или отсутствует пояс, пожалуйста, скажите сотруднику, что это брак. Так вы поможете нам бороться с недобросовестными покупателями и снизите риск того, что вам придет вещь с браком. 
+</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/1.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/2.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/3.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/4.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/5.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/6.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/7.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/8.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/9.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/10.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/11.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/12.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/13.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/14.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/15.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/16.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/17.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/18.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/19.webp,https://basket-19.wbcontent.net/vol3054/part305471/305471553/images/big/20.webp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Состав: натуральная шерсть 80%; полиэстер 20% | Цвет: коричневый | Пол: Женский | Сезон: демисезон | Вид застежки: пояс; пуговицы | Рост модели на фото: 165 см | Параметры модели на фото (ОГ-ОТ-ОБ): 85-60-90 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от -5°C до +15°С | Материал подкладки: вискоза - 70%, п/э - 30% | Покрой: прямой | Тип карманов: прорезные | Тип рукава: Длинный рукав прямого кроя | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: без элементов | Особенности модели: ветрозащита; двубортная; со шлицей | Уход за вещами: профессиональная химическая чистка в мягком режиме | Комплектация: Пальто - 1 шт; Плечики - 1 шт; Чехол - 1 шт; пояс - 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Befur</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/367672</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/287694148/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>287694148</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Полупальто шерстяное</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8804</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/304404090/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>304404090</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13078</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Befur</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/367672</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>76</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/370477912/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>370477912</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11523</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>M, S, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/288989036/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>288989036</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8417</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Черное полупальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в деловом стиле — удачное решение для офисного гардероба. Это сдержанная элегантность, уверенность и профессионализм. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://basket-18.wbcontent.net/vol2889/part288989/288989036/images/big/1.webp,https://basket-18.wbcontent.net/vol2889/part288989/288989036/images/big/2.webp,https://basket-18.wbcontent.net/vol2889/part288989/288989036/images/big/3.webp,https://basket-18.wbcontent.net/vol2889/part288989/288989036/images/big/4.webp,https://basket-18.wbcontent.net/vol2889/part288989/288989036/images/big/5.webp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Состав: шерсть натуральная 100% | Цвет: черный | Сезон: демисезон | Рост модели на фото: 175 см | Температурный режим: от -5 °C до +10 °C | Покрой: прямой | Воротник: отложной | Тип карманов: прорезные | Особенности модели: Без капюшона, теплый | Пол: Женский | Уход за вещами: Химическая стирка; стирка запрещена; отбеливание запрещено | Комплектация: 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>42</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/789426062/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>789426062</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Пальто пиджак шерстяное</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8092</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LULLA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/31355</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>XS, M, L</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>33</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/319080049/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>319080049</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11072</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/255231</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>L, M, S</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>89</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/292873097/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>292873097</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8030</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Коричневое полупальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/1.webp,https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/2.webp,https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/3.webp,https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/4.webp,https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/5.webp,https://basket-18.wbcontent.net/vol2928/part292873/292873097/images/big/6.webp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Состав: шерсть натуральная 100% | Цвет: серо-коричневый | Сезон: демисезон | Рост модели на фото: 175 см | Температурный режим: от -5 °C до +10 °C | Покрой: прямой | Воротник: отложной | Тип карманов: прорезные | Особенности модели: Без капюшона, теплый | Пол: Женский | Уход за вещами: Химическая стирка; стирка запрещена; отбеливание запрещено | Комплектация: 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>27</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/773082950/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>773082950</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Полупальто оверсайз из смесовой шерсти</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9772</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SELA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/5862</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>M, L</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/481144273/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>481144273</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное шоколадное</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>22140</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TRIUMF ST</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/312039</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M25" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/287694152/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>287694152</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8804</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XS, L, XL, XXL, S, M</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>41</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/775370787/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>775370787</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Пальто пиджак приталенное</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18273</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Eustera</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/867510</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>79</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M27" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/15323968/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>15323968</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>17438</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Предлагаем женское пальто, подходящее для межсезонья весной и осенью.
+Изготовлено из натуральной шерсти с добавлением вискозы и полиэстера, что обеспечивает удобство и долговечность при повседневном использовании.
+Модель прямого силуэта, который свободно сидит на разных типах фигуры.
+Высокая шлица сзади позволяет легко двигаться, а комбинированные целнокроеные рукава с ластовицей и подплечниками сохраняют аккуратную форму.
+Классический английский воротник и две горизонтальные кнопки придают изделию элегантность и надёжную фиксацию.
+Карманы в боковых швах, которые слегка смещены вперед, добавляют практичность, а пояс подчеркивает талию.
+Пальто оверсайз средней длины подходит для любого роста и создаёт актуальный образ.
+В нём вы будете чувствовать себя приятно и выглядеть привлекательно, соответствуя модным тенденциям.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/1.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/2.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/3.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/4.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/5.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/6.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/7.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/8.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/9.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/10.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/11.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/12.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/13.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/14.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/15.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/16.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/17.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/18.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/19.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/20.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/21.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/22.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/23.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/24.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/25.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/26.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/27.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/28.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/29.webp,https://basket-02.wbcontent.net/vol153/part15323/15323968/images/big/30.webp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 75%; вискоза 15%; терилен 10% | Цвет: бежевый; песочный | Пол: Женский | Сезон: Демисезон | Вид застежки: кнопки | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 84 - 58 - 88 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Покрой: прямой | Тип карманов: в шве | Тип рукава: цельнокроёный | Особенности модели: двубортная; дышащий материал; со шлицей | Уход за вещами: стирка запрещена; химчистка (сухая чистка); допускается отпаривание | Комплектация: пальто - 1шт; пояс - 1 шт; вешалка -1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Mmoda</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/37302</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 40</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>38</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M28" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/560649727/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>560649727</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Пальто натуральная шерсть с мехом лисы</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11431</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250047254</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>39</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/146055032/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>146055032</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Пальто мужское длинное демисезонное оверсайз синее</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5163</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Пальто мужское длинное синего цвета — это элегантная верхняя одежда для мужчин, юношей, подростков, которые ценят классический стиль и комфорт. Пальто мужское демисезонное утепленное выполнено из натуральной драповой ткани с добавлением шерсти, полиэстера и вискозы, с мягким подкладом с утеплителем ворсовым, что делает его тёплым, уютным и удобным для холодного периода времени года. Пальто мужское универсально: его можно носить зимой, в прохладную осень и ранней весной, сочетая с деловыми или кэжуал, спортивными, фэшн-образами.
+Пальто прямого кроя и удлиненной длины, с аккуратными плечами и широкими рукавами с разрезами по бокам и шлицей. Воротник-стойка с лацканами придаёт строгий стиль и классический акцент, а пуговицы делают образ завершённым и элегантным. Пальто мужское оверсайз свободно садится по фигуре и подходит для мужиков, парней, высоких, невысоких и больших размеров.
+Пальто мужское осеннее легко впишется в любой гардероб. Пальто мужское классическое, базовое, однотонное подчёркивает офисный, рабочий, школьный деловой стиль и гармонично сочетается с модным casual-образом с элементами евростиля. Такое брендовое дизайнерское решение уместно для офиса, учёбы, школы, студентов, прогулок, а в качестве праздничного, нарядного подарка молодежное пальто для мальчика, парня и мужа станет стильным и практичным выбором, находкой стилистов.
+Пальто мужское соединяет классику и современные тренды. Пальто мужское шерстяное отлично сохраняет тепло и форму, делает изделие долговечным, современный силуэт полупальто добавляет актуальности с вставками, карманами, фактурной тканью с ворсом. Качество пошива и подкладки подчёркивает премиальность бренда.
+Мужское пальто однобортное подойдёт для деловых встреч, работы, торжественных случаев, праздников и повседневной носки. Универсальное пальто, которое подчеркнёт индивидуальность, добавит образу уверенности и стиля, а главное — будет радовать многие сезоны.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/1.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/2.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/3.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/4.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/5.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/6.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/7.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/8.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/9.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/10.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/11.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/12.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/13.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/14.webp,https://basket-10.wbcontent.net/vol1460/part146055/146055032/images/big/15.webp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Состав: шерсть; полиэстер; шерсть 60% полиэстер 40% | Цвет: синий; темно-синий | Пол: Мужской | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 182 см | Параметры модели на фото (ОГ-ОТ-ОБ): 92-88-90 | Размер на модели: 46 | Утеплитель: шерсть | Температурный режим: от -10 °C до +10 °C | Материал подкладки: вискоза; полиэстер | Покрой: оверсайз | Тип карманов: прорезные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: пуговицы; оверсайз; длинное | Особенности модели: классическая модель; дышащий материал; однобортная | Уход за вещами: химическая чистка; химчистка | Комплектация: пальто | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BYDAY</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/65778</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>170-176/44, 170-176/54, 182-188/44, 182-188/46, 182-188/50, 182-188/52</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>11</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/749357736/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>749357736</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7655</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/146504</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>54</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/789426061/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>789426061</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Пальто пиджак шерстяное</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7009</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>LULLA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/31355</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>XS, S, M, L</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>39</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/330466210/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>330466210</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное натуральное</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12697</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Серое пальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет силуэт оверсайз. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Пальто в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbcontent.net/vol3304/part330466/330466210/images/big/1.webp,https://basket-20.wbcontent.net/vol3304/part330466/330466210/images/big/2.webp,https://basket-20.wbcontent.net/vol3304/part330466/330466210/images/big/3.webp,https://basket-20.wbcontent.net/vol3304/part330466/330466210/images/big/4.webp,https://basket-20.wbcontent.net/vol3304/part330466/330466210/images/big/5.webp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Состав: шерсть натуральная 100% | Цвет: серый | Пол: Женский | Сезон: демисезон | Рост модели на фото: 175 см | Температурный режим: от -5 °C до +10 °C | Покрой: оверсайз | Тип карманов: прорезные | Тип рукава: длинные | Особенности модели: Без капюшона, теплый | Уход за вещами: Химическая стирка; стирка запрещена; отбеливание запрещено | Комплектация: 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/749357735/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>749357735</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7862</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/146504</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>161</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/911457576/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>911457576</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12687</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>M, XL</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/107713204/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>107713204</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное прямое</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6170</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женское пальто весна-осень.
+Бежевое демисезонное пальто - отличный вариант для тех, кто ищет практичность, удобство и стиль. Эко-шуба с карманами подойдет для любого повседневного образа,а также впишется в любой гардероб делового стиля.  Длина пальто миди позволяет носить его как с платьем, так и с джинсами или брюками.
+Модель выполнена из высококачественного эко-меха. Теплая шерстяная ткань придаст ощущение уюта и комфорта весной или осенью. При изготовлении пальто использовались только премиум-ткани и высококачественная фурнитура. Отстрочка по всему изделию добавляет изюминки в классический стиль. 
+Женская верхняя одежда - показатель вкуса и стиля. Модное демисезонное пальто станет незаменимой вещью в гардеробе.
+Модель прямого кроя создает oversize эффект, поэтому подходит для беременных женщин. Пальто больших размеров. Застежка на кнопки, воротник стойка и карманы - удобство в каждой детали.
+Классический вариант женского полупальто придаст вашему образу стиля и лаконичности. При этом за счет воротника стойки , который застёгивается до конца, спасет от ветра и непогоды. Температурный режим от-5 до +10.
+</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/1.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/2.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/3.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/4.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/5.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/6.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/7.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/8.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/9.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/10.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/11.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/12.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/13.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/14.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/15.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/16.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/17.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/18.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/19.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/20.webp,https://basket-07.wbcontent.net/vol1077/part107713/107713204/images/big/21.webp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Состав: 64% шерсть, 26% акрил, 7% вискоза, 3% полиэстер | Цвет: бежевый; бежевый лайт; бежевый нейтральный; ванильно-бежевый; светло-бежевый | Пол: Женский | Сезон: Демисезон | Вид застежки: кнопки; Пришивные кнопки | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 88-63-95 | Размер на модели: 42 | Утеплитель: без утепления | Температурный режим: -5-+10 | Материал подкладки: полиэстер; вискоза; высококачественный полиэстер | Покрой: прямой | Тип карманов: прорезные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: без элементов | Особенности модели: Больше размеры для беременных модная модель | Уход за вещами: деликатная химическая чистка; допускается отпаривание | Комплектация: полупальто; вешалка; пакет | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5 LOVE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/705312</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>44, 46, 48, 50, 52, 54, 42, 56</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>127</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/723285888/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>723285888</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное классическое</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10082</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pudra Dress</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/82616</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 50</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>61</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/329473994/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>329473994</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Пальто короткое приталенное весна</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>9445</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женское пальто Befur – идеальный выбор для прохладной осени и ранней весны.  Модель выполнена из качественной ткани с добавлением натуральной шерсти, что обеспечивает комфорт и приятные тактильные ощущения. Двубортный крой с ветрозащитой надежно защитит от непогоды, а диагональный рисунок придает пальто стильный и современный вид. Прямой крой рукавов и прорезные карманы делают модель удобной в носке. Изготовленное из прочной смеси натуральной шерсти (80%) и полиэстера (20%), оно обеспечит вам комфорт и тепло в осенне-весенний период. Женское  пальто отлично подойдет как на весну, так и на осень и даже на начало зимы! Благодаря своему крою и размерной сетке идеально сядет на высоких и невысоких девушек и на беременных, будущих мам . Удобный пояс при желании легко сделает приталенное пальто. Верхняя одежда хорошо смотрится как со спортивными кроссовками, так и с модными высокими сапогами или с грубыми ботинками.
+Пальто Befur – это сочетание практичности, элегантности и комфорта.
+Обращайте внимание на оригинальный лейбл "Befur" и уникальный QR-код "Честный знак".
+Внимание! Если вам пришло изделие с браком или отсутствует пояс, пожалуйста, скажите сотруднику, что это брак. Так вы поможете нам бороться с недобросовестными покупателями и снизите риск того, что вам придет вещь с браком. 
+</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/1.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/2.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/3.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/4.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/5.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/6.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/7.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/8.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/9.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/10.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/11.webp,https://basket-20.wbcontent.net/vol3294/part329473/329473994/images/big/12.webp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Состав: натуральная шерсть 80%; полиэстер 20% | Цвет: черный | Пол: Женский | Сезон: демисезон | Вид застежки: пуговицы; кнопки | Рост модели на фото: 165 см | Параметры модели на фото (ОГ-ОТ-ОБ): 83-60-86 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Материал подкладки: вискоза - 70%, п/э - 30% | Покрой: прямой | Тип карманов: прорезные | Тип рукава: Длинный рукав прямого кроя | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: без элементов | Особенности модели: ветрозащита | Уход за вещами: профессиональная химическая чистка в мягком режиме | Комплектация: Пальто - 1 шт; Плечики - 1 шт; Чехол - 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Befur</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/367672</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>79</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M38" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/770695812/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>770695812</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>15357</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coressi</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>40</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/225889315/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>225889315</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Весеннее пальто в полоску длинное</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NARRATIVE</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/35512</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>M-L, S-M</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>20</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/946966983/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>946966983</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350412894</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/346320940/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>346320940</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное натуральное</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10968</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>M, XL</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/497508664/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>497508664</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное короткое жакет</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7509</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Lindo Gato</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/626100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>M, L, XL</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>17</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/752535253/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>752535253</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10388</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>M, L</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>14</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/595049394/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>595049394</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>6207</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>11</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/192213044/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>192213044</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Пальто классическое теплое на весну</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5560</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Пальто Бохо женское из ткани с содержанием натуральной шерсти (80%). Объемный текстильный материал на плотной трикотажной основе, имитирующий натуральный вьющийся мех - ягненка. Фактура на лицевой стороне образует завитки длинной 0,5 см. Сезон весна - осень 2026. Обладает достаточно хорошими теплоизоляционными свойствами, в нем не будет эффекта парника, отлично дышит и отводит влагу ничуть не хуже натурального меха благодаря шерстяным волокнам. Пальто Oversize предполагает свободную, широкую посадку, не стесняющую движения. Такой стиль нужно понимать и любить! Пальто Лёгкое, тёплое и приятное на ощупь станет для Вас хорошим решением на любой случай. Без подклада. До -10, но в холодную погоду его активно используют по верх жилета. Эко шубка,  экошуба, шуба барашек, шуба искусственная.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/1.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/2.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/3.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/4.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/5.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/6.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/7.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/8.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/9.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/10.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/11.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/12.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/13.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/14.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/15.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/16.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/17.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/18.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/19.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/20.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/21.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/22.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/23.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/24.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/25.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/26.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/27.webp,https://basket-13.wbcontent.net/vol1922/part192213/192213044/images/big/28.webp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 80%; Вискоза 20% | Цвет: латте; бежево-розовый; розовый | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 90-63-93 | Размер на модели: 48-52 | Утеплитель: без утеплителя | Температурный режим: от -10 °C до +15 °C | Материал подкладки: без подкладки | Покрой: прямой | Тип карманов: накладные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: пальто шуба женская зимняя; пальто больших размеров женское; пальто демисезонное женское больших размеров | Особенности модели: шуба чебурашка зимняя большие размеры; одежда на весну; Альпака | Уход за вещами: бережная стирка при 30 градусах; Деликатный отжим без перекручивания | Комплектация: пальто женское шерстяное оверсайз-1 шт; шубка барашек -1шт. | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>milidi</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/61696</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>oversize 54-62</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/775379354/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>775379354</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Пальто пиджак приталенное</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>18273</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Eustera</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/867510</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>46, 44, 42, 48</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>80</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M47" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/257303252/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>257303252</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8541</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Окунитесь в стиль и комфорт, выбирая женское пальто для сезона весна-осень 2026. Длина пальто по спинке - 63 см. Длина рукава - 63,5 см. Это короткое демисезонное пальто с воротником-стойкой станет вашим верным спутником в любое время года. Однобортное пальто прямого кроя. Воротник-стойка защитит Вас от прохладного ветра, втачные рукава обеспечивают лучшую посадку и комфорт при движении, глубокие карманы с листочкой, придают пальто уникальность, застежкой служат пришивные кнопки. Теплое укороченное ворсистое пальто привносит в образ изысканность, согреет вас даже в прохладные дни. Дизайнерская вещь подходит для девушек и женщин, ценящих как кэжуал стиль, так и офисную классику. Бежевый цвет подойдет к любому образу и станет незаменимой вещью в гардеробе автоледи. 
+Кашемировое внимание привлекается длинной линией и модным силуэтом - настоящее утончение 2026 года! Приталенное или оверсайз – выберите то, что подходит именно вам. Вариации размеров делают изделие доступным даже для подростков и невысоких девочек.
+Будьте уверены: ваше новое шерстяное полупальто не только подчеркнет вашу индивидуальность, но и подарит тепло. Смешивайте его с другими модными предметами вашего гардероба – ведь это ключ к созданию стильного ансамбля. Натуральная ворсовая ткань обеспечивает уют при каждом ношении.
+Ткань имеет ворсистую фактуру, так как в составе большой процент шерсти, из-за этого возможно прилипание волокна, шерсти животных и пыли. Ткань не скатывается, сохраняет цвет и форму. В процессе носки ворс ткани поднимается, поэтому рекомендуем очистить ворс липким роликом, пройтись велюровой щеткой по направлению ворса. Вся продукция бренда КОРЕССИ произведена по высоким стандартам, отшивается на новейшем швейном оборудовании, проходит качественный контроль. Производство Россия. Будем признательны оставленному отзыву! Приятных покупок!</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/1.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/2.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/3.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/4.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/5.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/6.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/7.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/8.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/9.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/10.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/11.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/12.webp,https://basket-16.wbcontent.net/vol2573/part257303/257303252/images/big/13.webp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 80%; вискоза 10%; полиэстер 10% | Цвет: бежевый; светло-бежевый | Пол: Женский | Сезон: демисезон | Вид застежки: кнопки | Рост модели на фото: 164 см | Параметры модели на фото (ОГ-ОТ-ОБ): 83-60-89 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Материал подкладки: полиэстер | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: застежка на кнопках; глубокие карманы с листочкой; Ворсовая ткань | Особенности модели: однобортная; ветрозащита; износостойкость | Уход за вещами: деликатная химическая чистка; допускается отпаривание | Комплектация: Пальто - 1 шт; Чехол с зип-пакетом или Упаковочная сумка-чемодан | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coressi</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>42, 48, 52</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M48" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/771425157/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>771425157</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7862</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/146504</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>84</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/329899819/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>329899819</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8016</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Окунитесь в стиль и комфорт, выбирая женское пальто для сезона весна-осень 2026. Длина пальто по спинке - 63 см. Длина рукава - 63,5 см. Это короткое демисезонное пальто с воротником-стойкой станет вашим верным спутником в любое время года. Однобортное пальто прямого кроя. Воротник-стойка защитит Вас от прохладного ветра, втачные рукава обеспечивают лучшую посадку и комфорт при движении, глубокие карманы с листочкой, придают пальто уникальность, застежкой служат пришивные кнопки. Теплое укороченное ворсистое пальто привносит в образ изысканность, согреет вас даже в прохладные дни. Дизайнерская вещь подходит для девушек и женщин, ценящих как кэжуал стиль, так и офисную классику. Серый цвет подойдет к любому образу и станет незаменимой вещью в гардеробе автоледи. 
+Кашемировое внимание привлекается длинной линией и модным силуэтом - настоящее утончение 2026 года! Приталенное или оверсайз – выберите то, что подходит именно вам. Вариации размеров делают изделие доступным даже для подростков и невысоких девочек.
+Будьте уверены: ваше новое шерстяное полупальто не только подчеркнет вашу индивидуальность, но и подарит тепло. Смешивайте его с другими модными предметами вашего гардероба – ведь это ключ к созданию стильного ансамбля. Натуральная ворсовая ткань обеспечивает уют при каждом ношении.
+Ткань имеет ворсистую фактуру, так как в составе большой процент шерсти, из-за этого возможно прилипание волокна, шерсти животных и пыли. Ткань не скатывается, сохраняет цвет и форму. В процессе носки ворс ткани поднимается, поэтому рекомендуем очистить ворс липким роликом, пройтись велюровой щеткой по направлению ворса. Вся продукция бренда КОРЕССИ произведена по высоким стандартам, отшивается на новейшем швейном оборудовании, проходит качественный контроль. Производство Россия. Будем признательны оставленному отзыву! Приятных покупок!</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/1.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/2.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/3.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/4.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/5.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/6.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/7.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/8.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/9.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/10.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/11.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/12.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/13.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/14.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/15.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/16.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/17.webp,https://basket-20.wbcontent.net/vol3298/part329899/329899819/images/big/18.webp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 80%; вискоза 10%; полиэстер 10% | Цвет: серый | Пол: Женский | Сезон: демисезон | Вид застежки: кнопки | Рост модели на фото: 164 см | Параметры модели на фото (ОГ-ОТ-ОБ): 83-60-89 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Материал подкладки: полиэстер | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: застежка на кнопках; глубокие карманы с листочкой; Ворсовая ткань | Особенности модели: однобортная; ветрозащита; износостойкость | Уход за вещами: деликатная химическая чистка; допускается отпаривание | Комплектация: Пальто - 1 шт; Упаковочная сумка-чемодан | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coressi</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M50" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/836686592/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>836686592</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Женское полупальто</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>8252</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>M, L, XXL</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/526167031/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>526167031</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Пальто женское весна-осень демисезонное</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3839</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LiBrand</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4162994</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>М, L, XL</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>21</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/914199141/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>914199141</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12653</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/493577428/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>493577428</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Весеннее шерстяное пальто на молнии</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5972</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250001823</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>50, 52</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M54" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/182534928/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>182534928</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4122</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Пальто женское длинное демисезонное имеет прямой крой и придется по душе ценителям классики. Пальто женское выполнено из натуральной шерсти, полиэстера и вискозы, комбинация которых создает ткань плотную, износостойкую и очень теплую. Подкладка из полиэстера сохраняет тепло и поддерживает оптимальный микроклимат. Пальто имеет широкий пояс и глубокие накладные карманы. Широкий отложной воротник смотрится элегантно и женственно, позволяет носить объемные платки и шарфы в зависимости от настроения и образа. Демисезонное пальто отлично подходит на каждый день и для особого случая. Женское пальто шерстяное создано для повседневной городской жизни, отдыха, поездок и путешествий. Универсальный песочный цвет комбинируется практически с любым гардеробом. Пальто женское шерсть имеет удобную длину до середины икры, защищает ноги от холода и при этом не сковывает движения. Широкий пояс визуально стройнит и подчеркивает талию. Изящные сапоги и полуботинки на каблуке или кроссовки на высокой подошве отлично комбинируются с такой моделью верхней одежды. Пальто женское длинное осеннее подходит также девушке или девочке подростку. Пальто женское с поясом незаменимо для прогулок и поездки, путешествий. Удобное и практичное демисезонное пальто можно надевать на работу, на встречу с друзьями, на учебу в университет или школу, для посещения культурных мероприятий. Пальто длинное идеально подходит в качестве базовой модели верхнего гардероба.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/1.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/2.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/3.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/4.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/5.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/6.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/7.webp,https://basket-12.wbcontent.net/vol1825/part182534/182534928/images/big/8.webp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Состав: Натуральная шерсть; полиэстер; вискоза | Цвет: песочный | Пол: Женский | Вид застежки: без застежки | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 85 63 90 | Размер на модели: S | Материал подкладки: ПЭ | Комплектация: Пальто - 1 шт | Страна производства: Китай</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>THOMAS MUNZ</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/27600</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>L, M, S</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M55" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/311905357/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>311905357</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Полупальто пиджак блейзер оверсайз короткое</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11556</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Почему без подкладки? Это-фишка!
+Именно так наше полупальто становится идеальным межсезонным героем: его можно носить поверх любой одежды, оно невесомое, но теплое за счет 100% шерсти, и вы сможете носить его с начала сентября до поздней осени и с первой капели весной. Это свобода, универсальность и умный подход к гардеробу.
+Пальто из 100% натуральной шерсти без подклада имеет ряд преимуществ:
+▌ Терморегуляция
+Шерсть обладает отличными теплоизоляционными свойствами благодаря своей структуре волокон. Она удерживает тепло тела зимой и позволяет коже дышать летом, обеспечивая комфорт в любую погоду.
+▌ Прочность и долговечность
+Натуральная шерсть прочнее синтетики и способна выдерживать длительное использование без потери формы и качества. Это делает пальто долговечным и надежным вложением.
+▌ Комфорт и воздухопроницаемость
+Без подкладки кожа лучше дышит, предотвращая перегрев и потливость. Это особенно важно в межсезонье, когда погода нестабильная.
+▌ Экологичность
+Использование натуральных материалов способствует снижению негативного воздействия на окружающую среду. Шерсть биоразлагаема и возобновляема, что снижает углеродный след производства.
+Представляем вам стильное и универсальное полупальто от Roman fashion, которое станет незаменимым элементом вашего гардероба! Эта модель, выполненная из 100% шерсти, подарит вам комфорт и тепло в прохладную весеннюю или осеннюю погоду. Классический крой в стиле оверсайз с двубортной застежкой на пуговицах придает образу элегантность и современный шик.  Благодаря дышащему материалу вы будете чувствовать себя комфортно в любой ситуации.  
+Короткая длина пальто идеально подходит для невысоких и высоких девушек, подчеркивая стройность силуэта. Длинные рукава и отсутствие капюшона добавляют модели изысканности и женственности.  Ворсистая фактура шерсти придает пальто уютный и тактильно приятный вид.  Пальто тонкое и при этом очень теплое.
+</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/1.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/2.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/3.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/4.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/5.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/6.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/7.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/8.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/9.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/10.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/11.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/12.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/13.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/14.webp,https://basket-19.wbcontent.net/vol3119/part311905/311905357/images/big/15.webp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Состав: 100 % шерсть | Цвет: светло-серый; серый | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 167 см | Параметры модели на фото (ОГ-ОТ-ОБ): 80-63-91 | Размер на модели: S | Утеплитель: шерсть | Температурный режим: от +5 °C до +15 °C | Материал подкладки: без подкладки | Покрой: свободный | Тип карманов: прорезные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: пуговицы | Особенности модели: двубортная; дышащий материал | Комплектация: пальто</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/255231</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>L, M, S</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>24</v>
+      </c>
+      <c r="L56" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M56" t="n">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/771001071/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>771001071</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4607</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SerpikovaNS</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1402110</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>43</v>
+      </c>
+      <c r="L57" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/785074282/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>785074282</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Женское полупальто</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10536</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>M, L</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M58" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/15323969/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>15323969</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15016</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Предлагаем женское пальто, подходящее для межсезонья весной и осенью.
+Изготовлено из натуральной шерсти с добавлением вискозы и полиэстера, что обеспечивает удобство и долговечность при повседневном использовании.
+Модель прямого силуэта, который свободно сидит на разных типах фигуры.
+Высокая шлица сзади позволяет легко двигаться, а комбинированные целнокроеные рукава с ластовицей и подплечниками сохраняют аккуратную форму.
+Классический английский воротник и две горизонтальные кнопки придают изделию элегантность и надёжную фиксацию.
+Карманы в боковых швах, которые слегка смещены вперед, добавляют практичность, а пояс подчеркивает талию.
+Пальто оверсайз средней длины подходит для любого роста и создаёт актуальный образ.
+В нём вы будете чувствовать себя приятно и выглядеть привлекательно, соответствуя модным тенденциям.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/1.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/2.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/3.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/4.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/5.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/6.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/7.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/8.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/9.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/10.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/11.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/12.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/13.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/14.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/15.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/16.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/17.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/18.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/19.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/20.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/21.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/22.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/23.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/24.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/25.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/26.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/27.webp,https://basket-02.wbcontent.net/vol153/part15323/15323969/images/big/28.webp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 75%; вискоза 15%; терилен 10% | Цвет: кэмел; коричневый | Пол: Женский | Сезон: Демисезон | Вид застежки: кнопки | Рост модели на фото: 170 см | Параметры модели на фото (ОГ-ОТ-ОБ): 84 - 58 - 88 | Размер на модели: 42 | Утеплитель: без утеплителя | Температурный режим: от 0 °C до +15 °C | Материал подкладки: вискоза 53%; полиэстер 47% | Покрой: свободный | Тип карманов: в шве | Тип рукава: цельнокроёный | Опции капюшона: без капюшона | Опции опушки: без опушки | Особенности модели: двубортная; дышащий материал; со шлицей | Уход за вещами: стирка запрещена; химчистка (сухая чистка) | Комплектация: пальто - 1шт; пояс - 1шт; Вешалка - 1шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mmoda</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/37302</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>44, 40</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M59" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/914196635/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>914196635</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Женское полупальто</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6522</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/770729449/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>770729449</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Пальто короткое из натуральной шерсти</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8599</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Suerte more</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250020687</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>107</v>
+      </c>
+      <c r="L61" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/771628051/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>771628051</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Пальто из шерсти альпака демисезонное</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>52745</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/25326</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/805106976/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>805106976</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Пальто с шарфом 100% шерсть короткое большие размеры</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>14098</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Стильное шерстяное пальто с шарфом из 100% шерсти станет незаменимым элементом вашего осенне-весеннего гардероба. Двубортный крой и английский воротник придают модели лаконичный и элегантный вид, а оверсайз силуэт обеспечивает комфорт и свободу движений, а также подходит для женщин до 58-60 размера. Пальто дополнено съемным шарфом, который можно использовать как самостоятельный аксессуар.  Модель прекрасно подойдет как для офиса, так и для вечерних прогулок.  Благодаря натуральному составу из шерсти, пальто прекрасно сохраняет тепло при температуре от 0 °C до +15 °C.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/1.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/2.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/3.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/4.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/5.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/6.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/7.webp,https://basket-37.wbcontent.net/vol8051/part805106/805106976/images/big/8.webp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Состав: шерсть | Цвет: графит; черный графит; стальной графит; черный | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Температурный режим: от 0 °C до +15 °C | Покрой: оверсайз | Тип карманов: накладные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: шарф | Особенности модели: двубортная | Уход за вещами: деликатная химическая чистка | Комплектация: шарф 1шт.; Пальто короткое шерстяное 1шт.; Вешалка 1шт.; чехол 1шт.; Зип-пакет 1шт. | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/116400</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>L oversize, M oversize, S oversize</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M63" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/197262900/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>197262900</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное оверсайз теплое длинное</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>7750</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пальто демисезонное женское идеально подходит для тех, кто ищет верхнюю одежду, которая будет актуальна как в весенний, так и в осенний период.Это длинная, теплая, демисезонная модель предназначена для женщин, которые ценят стиль и комфорт в верхней одежде. Оно отлично подходит для весенне-осеннего периода, когда погода может быть непредсказуемой. Пальто сочетает в себе элегантный дизайн и функциональность, что делает его универсальным вариантом для повседневного ношения.
+Основное предназначение этой модели — защита от холода и ветра в межсезонье. Оно выполнено из высококачественных шерстяных материалов, что обеспечивает тепло и комфорт даже в прохладные дни. Модель имеет классическую форму, что позволяет легко комбинировать ее с различными нарядами, будь то офисный стиль или повседневный образ.  цвет делает его особенно стильным и универсальным, позволяя сочетать его с разнообразной одеждой. Пояс идет в комплекте. Очень удобные и глубокие карманы. 
+Длинный крой обеспечивает дополнительное тепло, а также создает аккуратный силуэт. Мягкая шерсть в составе материала обеспечивает приятные ощущения при носке. В этом пальто вы будете выглядеть стильно и ощущать себя комфортно в любых условиях.
+Модель отлично подойдет для городских прогулок, деловых встреч или встреч с друзьями. Пальто женское весна-осень легко можно дополнить шарфом или шапкой, что сделает ваш образ завершенным. Оно станет надежным спутником в вашем гардеробе, добавив в него ярких акцентов и создавая множество стильных образов.
+</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/1.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/2.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/3.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/4.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/5.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/6.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/7.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/8.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/9.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/10.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/11.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/12.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/13.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/14.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/15.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/16.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/17.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/18.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/19.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/20.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/21.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/22.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/23.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/24.webp,https://basket-13.wbcontent.net/vol1972/part197262/197262900/images/big/25.webp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Состав: 50% шерсть, 30% вискоза, 20% поливискоза | Цвет: серый; натуральный серый; зернистый светло-серый | Пол: Женский | Сезон: демисезон | Вид застежки: пуговицы; супатная | Рост модели на фото: 177 см | Параметры модели на фото (ОГ-ОТ-ОБ): 86-64-93 | Размер на модели: 46 | Утеплитель: без утеплителя | Температурный режим: от +3 до +15 | Материал подкладки: полиэстер | Покрой: оверсайз | Тип карманов: накладные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: карманы | Особенности модели: ветрозащита | Уход за вещами: допускается отпаривание; деликатная химическая чистка | Комплектация: пояс; пальто | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>EURYDIKE</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/3971567</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>22</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M64" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/537146660/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>537146660</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>8013</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M65" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/541448913/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>541448913</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>9271</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>156</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M66" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/825019950/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>825019950</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13449</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Стильное женское весеннее пальто из шерсти в насыщенном цвете станет акцентом вашего демисезонного гардероба. Это приталенное пальто гармонично сочетает в себе минимализм и практичность. Благодаря удлинённому силуэту модель визуально вытягивает фигуру, а воротник стойка защитит от холода и создаст цельный, аккуратный силуэт.
+Четкая линия плеч и полуприталенный крой делают изделие комфортным для повседневной носки, а широкий пояс позволяет регулировать посадку и подчёркивать талию. Удобные карманы с клапаном добавляют практичности, сохраняя эстетику минимализма.
+Это шерстяное пальто женское выполнено из плотной натуральной ткани, которая хорошо держит форму и сохраняет тепло. Пальто удлинённое шерстяное скрасит вам любой образ и станет идеальным выбором для весенне-осеннего периода.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/1.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/2.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/3.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/4.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/5.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/6.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/7.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/8.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/9.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/10.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/11.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/12.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/13.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/14.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/15.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/16.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/17.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/18.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/19.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/20.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/21.webp,https://basket-37.wbcontent.net/vol8250/part825019/825019950/images/big/22.webp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 80%; вискоза 15%; Эластан 5% | Цвет: темно-коричневый; шоколадный | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 174 см | Параметры модели на фото (ОГ-ОТ-ОБ): 83-60-90 | Размер на модели: 44 | Температурный режим: от -5 °C до +10 °C | Материал подкладки: Полиэстер 100 % | Покрой: приталенный | Тип карманов: с клапаном | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: Длинное демисезонное Пальто весна осень; Драповое из шерсти на осень и весну; Осеннее и весеннее для девушек и женщин | Особенности модели: офисный стиль; Классическое с поясом; Удлинённый силуэт | Уход за вещами: деликатная химическая чистка; не гладить; машинная стирка запрещена | Комплектация: Пальто женское – 1 шт; Пояс – 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/146504</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>151</v>
+      </c>
+      <c r="L67" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/874597322/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>874597322</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное шерстяное классическое с поясом</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5174</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Milens</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/109326</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>36</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/927984772/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>927984772</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12687</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/333388543/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>333388543</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11523</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>L, XS, S, M, XL</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>25</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/497552528/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>497552528</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное короткое жакет</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7162</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Lindo Gato</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/626100</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>L, M, XL</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>155</v>
+      </c>
+      <c r="L71" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M71" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/312616259/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>312616259</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12332</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Серое пальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 5 до минус 10.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Пальто в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/1.webp,https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/2.webp,https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/3.webp,https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/4.webp,https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/5.webp,https://basket-19.wbcontent.net/vol3126/part312616/312616259/images/big/6.webp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Состав: шерсть мериноса 100% | Цвет: серый | Пол: Женский | Сезон: демисезон | Температурный режим: от -5 °C до +10 °C | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Особенности модели: Без капюшона, теплый | Уход за вещами: Химическая стирка; стирка запрещена; отбеливание запрещено | Комплектация: 1 шт | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>S, M, L</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>11</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/543691598/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>543691598</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>пальто шерстяное длинное с жилеткой</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5542</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>4</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/849729060/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>849729060</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13713</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>S, M, L, XL</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>26</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/502427212/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>502427212</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4607</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SerpikovaNS</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1402110</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/493989817/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>493989817</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Пальто зимнее длинное с люрексом без пояса натуральный мех</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>17046</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Элегант</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/40236</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>164-100-110, 164-104-114, 164-108-118, 164-116-126, 164-120-130, 164-124-134, 164-128-138, 164-96-106, 164-92-102</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>24</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M76" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/901739148/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>901739148</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>пальто</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350349026</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/297712814/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>297712814</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное длинное без подкладки</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>28235</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Элегантное демисезонное пальто от OKSANA UTOVA BRAND в глубоком коричневом цвете - это квинтэссенция стиля и безупречного качества. Модель выполнена из натуральной шерсти, что делает это драповое изделие незаменимой базой для создания дорогих образов в межсезонье. Авторский дизайн длины макси и безупречный прямой крой с застежкой на одну пуговицу подчеркивают лаконичный силуэт и визуально вытягивают фигуру. В комплекте предусмотрен изысканный шарф, который обеспечивает дополнительный комфорт и тепло в ветреную весеннюю погоду.
+Свободный фасон оверсайз не сковывает движений, позволяя комбинировать верхнюю одежду с повседневными вещами. Широкая размерная сетка, включающая большие размеры, гарантирует идеальную посадку для женщин с любым типом фигуры, а премиальная шерстяная ткань обеспечивает долговечность и износостойкость.
+Данное классическое пальто - яркий представитель трендов 2026 года, где функциональность встречается с эксклюзивным исполнением. Оно станет идеальным выбором для деловых встреч, городских прогулок или торжественных выходов, подчеркивая статус и тонкий вкус своей обладательницы. Инвестируйте в брендовый гардероб, чтобы чувствовать себя уверенно и выглядеть изысканно в любой ситуации, будь то работа или вечернее мероприятие.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/1.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/2.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/3.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/4.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/5.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/6.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/7.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/8.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/9.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/10.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/11.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/12.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/13.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/14.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/15.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/16.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/17.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/18.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/19.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/20.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/21.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/22.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/23.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/24.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/25.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/26.webp,https://basket-18.wbcontent.net/vol2977/part297712/297712814/images/big/27.webp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 100% | Цвет: темный горький шоколад; горький шоколад; шоколадный трюфель; коричневый меланж | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 173 см | Параметры модели на фото (ОГ-ОТ-ОБ): 97-75-112 | Размер на модели: S | Утеплитель: без утеплителя | Температурный режим: от +5 °C до -15 °C | Материал подкладки: без подкладки | Покрой: оверсайз | Тип карманов: потайные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: без элементов | Особенности модели: съемный шарф | Уход за вещами: гладить при t не более 110°C; химическая чистка; сушка в горизонтальном положении | Комплектация: пальто | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>OKSANA UTOVA BRAND</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/814984</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2XL, L, S, XL, 3XL</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>21</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M78" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/488387892/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>488387892</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Пальто длинное оверсайз весна-осень</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>4150</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>HANBIYKE</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1304162</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>L, M, S, XL</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>24</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/325024418/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>325024418</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Пальто осеннее короткое</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>4547</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>5 LOVE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/705312</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/482254030/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>482254030</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Пальто пиджак оверсайз серое женское из 100% шерсти</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3839</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Harizmic</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/363171</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ONESIZE</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>41</v>
+      </c>
+      <c r="L81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M81" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/267900794/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>267900794</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное длинное без подкладки</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>28235</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Элегантное демисезонное пальто от OKSANA UTOVA BRAND в графитовом цвете - это квинтэссенция стиля и безупречного качества. Модель выполнена из натуральной шерсти, что делает это драповое изделие незаменимой базой для создания дорогих образов в межсезонье. Авторский дизайн длины макси и безупречный прямой крой с застежкой на одну пуговицу подчеркивают лаконичный силуэт и визуально вытягивают фигуру. В комплекте предусмотрен изысканный шарф, который обеспечивает дополнительный комфорт и тепло в ветреную весеннюю или осеннюю погоду.
+Свободный фасон оверсайз не сковывает движений, позволяя комбинировать верхнюю одежду как со строгими офисными костюмами, так и с повседневными вещами в стиле. Благодаря универсальному серому оттенку и прямым линиям, вещь легко вписывается в эстетику аристократичной элегантности. Широкая размерная сетка, включающая большие размеры, гарантирует идеальную посадку для женщин с любым типом фигуры, а премиальная шерстяная ткань обеспечивает долговечность и износостойкость.
+Классическое пальто - яркий представитель трендов 2026 года, где функциональность встречается с эксклюзивным исполнением. Оно станет идеальным выбором для деловых встреч, городских прогулок или торжественных выходов, подчеркивая статус и тонкий вкус своей обладательницы. Инвестируйте в брендовый гардероб, чтобы чувствовать себя уверенно и выглядеть изысканно в любой ситуации, будь то работа или вечернее мероприятие.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/1.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/2.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/3.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/4.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/5.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/6.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/7.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/8.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/9.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/10.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/11.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/12.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/13.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/14.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/15.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/16.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/17.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/18.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/19.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/20.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/21.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/22.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/23.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/24.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/25.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/26.webp,https://basket-17.wbcontent.net/vol2679/part267900/267900794/images/big/27.webp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 100% | Цвет: серый; серый металлик; серый гранит; серо-черный; серый меланж | Пол: Женский | Сезон: Демисезон | Вид застежки: пуговицы | Рост модели на фото: 173 см | Параметры модели на фото (ОГ-ОТ-ОБ): 97-75-112 | Размер на модели: S | Утеплитель: без утеплителя | Температурный режим: от +5 °C до -15 °C | Материал подкладки: без подкладки | Покрой: оверсайз | Тип карманов: потайные | Тип рукава: длинные | Опции капюшона: без капюшона | Опции опушки: без опушки | Декоративные элементы: без элементов | Особенности модели: съемный шарф | Уход за вещами: гладить при t не более 110°C; химическая чистка; сушка в горизонтальном положении | Комплектация: пальто; Шарф | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OKSANA UTOVA BRAND</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/814984</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>L, M, S, XL, 2XL, 3XL</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>56</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M82" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/826929939/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>826929939</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2577</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Женское пальто – это стильная модель с прямым кроем, которая подчеркнет вашу утонченность и элегантность. Пальто для женщин идеально подойдет для весны и осени и поможет создать изящный образ.
+Пояс акцентирует талию, создавая утонченный силуэт. Наличие карманов добавляет функциональности, не нарушая гармонии образа. Такое осеннее пальто идеально подойдет женщине, которая ценит высокое качество и классические детали в современном исполнении.Благодаря материалу и крою пальто на весну становится универсальным решением как для делового, так и для вечернего выхода. Это демисезонное пальто — идеальный выбор для теплой осени и весны. Высокое качество пошива подчеркивает статусность и внимание к деталям, а твидовая текстура придает изделию особую глубину цвета и визуальный интерес.Пальто весна осень отлично сочетается с различными аксессуарами и одеждой, позволяя создавать разнообразные образы — от строгих до романтичных. Это идеальный выбор для тех, кто ищет баланс между комфортом и изысканностью в демисезонном гардеробе.Такое пальто с поясом станет незаменимой частью гардероба для тех, кто хочет подчеркнуть индивидуальность через элегантные детали и продуманный крой. Модель отвечает всем требованиям современного стиля. Выбирая это демисезонное пальто, вы получаете идеальное сочетание качества, комфорта и эстетики для создания неповторимого образа.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/1.webp,https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/2.webp,https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/3.webp,https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/4.webp,https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/5.webp,https://basket-37.wbcontent.net/vol8269/part826929/826929939/images/big/6.webp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Состав: Полиэстер 65%, хлопок 35% | Цвет: коричневый | Пол: Женский | Сезон: Демисезон | Вид застежки: кнопки | Утеплитель: без утеплителя | Температурный режим: от -5 °C до +10 °C | Материал подкладки: без подкладки | Покрой: прямой | Тип карманов: накладные | Тип рукава: длинный | Опции капюшона: без капюшона | Опции опушки: без опушки | Мех опушки/отделки: без опушки | Декоративные элементы: без элементов | Особенности модели: дышащий материал | Уход за вещами: ручная стирка при t не более 30 С; гладить при t не более 110°C | Комплектация: пояс - 1 шт; Пальто женское - 1 шт | Страна производства: Китай</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>YFH</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250033719</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/505531759/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>505531759</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Двубортное пальто из драпа с содержанием шерсти</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>5738</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SELA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/5862</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M84" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/723231379/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>723231379</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное классическое</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10082</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Pudra Dress</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/82616</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>123</v>
+      </c>
+      <c r="L85" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M85" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/863745972/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>863745972</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Пальто женское шерстяное классическое длинное демисезонное</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5693</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>KENAN</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/50899</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>50, 62, 52, 54, 56, 58, 60, 64, 66</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>107</v>
+      </c>
+      <c r="L86" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/488387893/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>488387893</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень макси в полоску</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4204</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>HANBIYKE</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1304162</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>L, M, S, XL</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>86</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M87" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/287755147/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>287755147</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Пальто двубортное драповое с шерстью демисезонное</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3688</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Befree</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/5862</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>M/170, L/170</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M88" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/541444324/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>541444324</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>9941</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250000954</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M89" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/163566992/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>163566992</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Пальто весеннее шерстяное кимоно без подклада оверсайз</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>7779</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Самое весеннее женское пальто с  цветочным принтом!
+Легкое, но при этом теплое, потому что содержит натуральную шерсть в составе.
+Пальто кимоно с поясом - классика в новом исполнении.
+Вязаное уютное демисезонное пальто-кардиган идеальный выбор для весенней осенней погоды. Даже летом это пальто без подклада можно надеть прохладными вечерами.
+Черное пальто-кардиган с изысканным рисунком, впишется в любой образ в гардероб весна-осень. 
+Благодаря прямому крою идеально сидит на любой фигуре. Посадка легкий оверсайз дарит комфорт на весь день и подходит беременным девушкам и для женщин больших размеров плюс size. 
+Вывязанный рисунок и безупречный пошив  делают это пальто-жакет шикарным! Оно несомненно станет вашим любимым! Его можно стирать в стиральной машине и носить долгие годы. 
+Обновите  свой гардероб качественной и стильной  одеждой от бренда VESHALKA ! 
+</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/1.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/2.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/3.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/4.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/5.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/6.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/7.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/8.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/9.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/10.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/11.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/12.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/13.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/14.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/15.webp,https://basket-11.wbcontent.net/vol1635/part163566/163566992/images/big/16.webp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Состав: шерсть 30%; акрил 70% | Цвет: черный | Пол: Женский | Сезон: Демисезон | Вид застежки: пояс | Рост модели на фото: 156 см | Размер на модели: 42-44 | Утеплитель: без утеплителя | Температурный режим: от +10 °C до +15 °C | Материал подкладки: без подкладки | Покрой: прямой | Тип карманов: накладные | Тип рукава: длинные | Особенности модели: для высоких | Уход за вещами: стирка при t не более 30°C | Комплектация: пальто весеннее женское | Страна производства: Киргизия</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>VESHALKA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1287074</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>42-44, 46-48, 50-52</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>42</v>
+      </c>
+      <c r="L90" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M90" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/172909482/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>172909482</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Пальто из шерсти альпака демисезонное двубортное</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>39310</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Элегантное демисезонное пальто от российского бренда KROYYORK из высококачественной смеси сури альпака и натуральной овечьей шерсти. Благодаря ворсистой структуре материал напоминает кашемировое – износостойкое и мягкое долгое время.
+Модель прямого силуэта с классическим английским воротником и длиной 108 см, что отлично подходит для демисезонных периодов. Спущенные рукава придают изделию современный вид, а застежка на пуговицы и прорезные карманы с листочкой добавляют элегантности. Пальто комплектуется поясом в тон для создания более женственного образа. 
+Внутренняя подкладка из вискозы приятна к телу и не электризуется. У этой верхней одежды весна-осень свободный крой и безупречное качество исполнения. В нашем ассортименте представлены большие размеры.
+Природное волокно с высокой прочностью, обеспечивающее долговечность вещи и сохранение формы даже после многократной носки. Модное пальто из альпаки выглядит изящно, сохраняя при этом практичность и комфорт. Благодаря мягкости и гипоаллергенным свойствам, оно идеально подойдет для весеннего гардероба.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/1.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/2.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/3.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/4.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/5.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/6.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/7.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/8.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/9.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/10.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/11.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/12.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/13.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/14.webp,https://basket-12.wbcontent.net/vol1729/part172909/172909482/images/big/15.webp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Состав: шерсть альпака 70%; шерсть овечья 20%; Шерсть 10% | Цвет: ванильно-бежевый; бежевый | Сезон: демисезон | Вид застежки: пуговицы; пояс | Рост модели на фото: 168 см | Параметры модели на фото (ОГ-ОТ-ОБ): 87-72-97 | Размер на модели: 42 | Утеплитель: нет | Температурный режим: от +10 °C до -5 °C | Материал подкладки: Вискоза - 100% | Покрой: прямой | Тип карманов: прорезные | Тип рукава: длинные | Опции опушки: без опушки | Декоративные элементы: отделочные строчки | Особенности модели: с подкладкой; гипоаллергенный материал; двубортная | Конструктивные элементы: с подкладкой | Пол: Женский | Уход за вещами: деликатная химическая чистка; рекомендуется применение отпаривателя | Комплектация: Пояс - 1 шт.; Пальто женское весна осень шерстяное - 1 шт. | Страна производства: Россия</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/25326</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>9</v>
+      </c>
+      <c r="L91" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M91" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/560658481/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>560658481</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Пальто натуральная шерсть с мехом лисы</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11431</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250047254</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>24</v>
+      </c>
+      <c r="L92" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/733139850/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>733139850</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>13449</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>BUTALABEL</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/146504</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>132</v>
+      </c>
+      <c r="L93" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M93" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/723288591/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>723288591</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное классическое</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10511</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Pudra Dress</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/82616</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>77</v>
+      </c>
+      <c r="L94" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M94" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/366417626/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>366417626</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Короткое шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>9413</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>S, L, XXL, M, XL</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>9</v>
+      </c>
+      <c r="L95" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M95" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/695321729/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>695321729</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Пальто весеннее шерстяное без подклада</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>14836</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CORITSA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/686200</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>46-48, 50-52, 54-56</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/886433950/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>886433950</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350063173</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/710143091/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>710143091</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4667</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250083754</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>71</v>
+      </c>
+      <c r="L98" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M98" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/782744628/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>782744628</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>9411</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4394807</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>48, 56</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>4</v>
+      </c>
+      <c r="L99" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/836687106/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>836687106</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12671</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>MAISON DAVID</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>M, L</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>39</v>
+      </c>
+      <c r="L100" t="n">
+        <v>5</v>
+      </c>
+      <c r="M100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/14718163/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>14718163</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Английское пальто из натуральной шерсти Classic</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>25632</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Женский дафлкот (duffle coat) Оriginal Montgomery Classic классического кроя на четырёх пуговицах. Качество от производителя с 1896 года. На ярлыке каждого дафлкота Original Montgomery написано "The world's oldest duffel coat company. Made with pride in England". И это не пустые слова. Компания Original Montgomery является самым первым производителем дафлкотов в мире. Каждый обладатель этих пальто может быть на 100% уверен в их исключительном качестве. Петли застёжек сделаны из качественной натуральной кожи, пуговицы-клыки из рога. Женская модель дафлкота Classic Duffle имеет скрытую молнию дополнительно к застёжкам-клыкам. Капюшон удобно регулируется ремешками и пуговицами и может застегиваться для дополнительной защиты от ветра и дождя.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/1.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/2.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/3.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/4.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/5.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/6.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/7.webp,https://basket-02.wbcontent.net/vol147/part14718/14718163/images/big/8.webp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Состав: полиэстер 30%; шерсть овцы 70% | Цвет: алый; вишневый | Сезон: демисезон | Температурный режим: от +5 °C до -15 °C | Страна производства: Великобритания | Опции капюшона: несъемный капюшон | Тип карманов: накладные | Пол: Женский | Комплектация: чехол; вешалка; дафлкот | Уход за вещами: стирка запрещена; химическая чистка</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Original Montgomery</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/51480</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>30, 46, 44</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M101" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
